--- a/artfynd/A 20004-2024 artfynd.xlsx
+++ b/artfynd/A 20004-2024 artfynd.xlsx
@@ -2276,10 +2276,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117579701</v>
+        <v>117579646</v>
       </c>
       <c r="B17" t="n">
-        <v>91962</v>
+        <v>91772</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2288,25 +2288,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2319,10 +2319,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>482297</v>
+        <v>482363</v>
       </c>
       <c r="R17" t="n">
-        <v>6918898</v>
+        <v>6918799</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2382,10 +2382,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117579646</v>
+        <v>117579701</v>
       </c>
       <c r="B18" t="n">
-        <v>91772</v>
+        <v>91962</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2394,25 +2394,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2425,10 +2425,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>482363</v>
+        <v>482297</v>
       </c>
       <c r="R18" t="n">
-        <v>6918799</v>
+        <v>6918898</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2594,10 +2594,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117579809</v>
+        <v>117579661</v>
       </c>
       <c r="B20" t="n">
-        <v>79069</v>
+        <v>90648</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2606,25 +2606,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229821</v>
+        <v>1503</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2637,10 +2637,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>482297</v>
+        <v>482261</v>
       </c>
       <c r="R20" t="n">
-        <v>6918901</v>
+        <v>6918909</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2700,10 +2700,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117579661</v>
+        <v>117579645</v>
       </c>
       <c r="B21" t="n">
-        <v>90648</v>
+        <v>91772</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2712,25 +2712,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>482261</v>
+        <v>482353</v>
       </c>
       <c r="R21" t="n">
-        <v>6918909</v>
+        <v>6918745</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2806,10 +2806,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117579645</v>
+        <v>117579809</v>
       </c>
       <c r="B22" t="n">
-        <v>91772</v>
+        <v>79069</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2818,25 +2818,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>482353</v>
+        <v>482297</v>
       </c>
       <c r="R22" t="n">
-        <v>6918745</v>
+        <v>6918901</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 20004-2024 artfynd.xlsx
+++ b/artfynd/A 20004-2024 artfynd.xlsx
@@ -788,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117579915</v>
+        <v>117579697</v>
       </c>
       <c r="B3" t="n">
-        <v>78216</v>
+        <v>91962</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,21 +804,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482356</v>
+        <v>482321</v>
       </c>
       <c r="R3" t="n">
-        <v>6918816</v>
+        <v>6918867</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,17 +887,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu, Marielle Löthman</t>
+          <t>Marielle Löthman, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117579880</v>
+        <v>117579975</v>
       </c>
       <c r="B4" t="n">
-        <v>90464</v>
+        <v>78217</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -906,25 +906,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>482357</v>
+        <v>482221</v>
       </c>
       <c r="R4" t="n">
-        <v>6918836</v>
+        <v>6918908</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,17 +993,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu, Marielle Löthman</t>
+          <t>Marielle Löthman, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117579813</v>
+        <v>117579646</v>
       </c>
       <c r="B5" t="n">
-        <v>78514</v>
+        <v>91772</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,25 +1012,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1043,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>482200</v>
+        <v>482363</v>
       </c>
       <c r="R5" t="n">
-        <v>6918933</v>
+        <v>6918799</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,10 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117579652</v>
+        <v>117579809</v>
       </c>
       <c r="B6" t="n">
-        <v>78125</v>
+        <v>79069</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1122,21 +1122,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1149,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>482237</v>
+        <v>482297</v>
       </c>
       <c r="R6" t="n">
-        <v>6918837</v>
+        <v>6918901</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,10 +1212,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117579703</v>
+        <v>117579655</v>
       </c>
       <c r="B7" t="n">
-        <v>79098</v>
+        <v>90425</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1228,21 +1228,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>3242</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482319</v>
+        <v>482226</v>
       </c>
       <c r="R7" t="n">
-        <v>6918649</v>
+        <v>6918856</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,10 +1318,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117579655</v>
+        <v>117579701</v>
       </c>
       <c r="B8" t="n">
-        <v>90425</v>
+        <v>91962</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1334,21 +1334,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3242</v>
+        <v>2079</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>482226</v>
+        <v>482297</v>
       </c>
       <c r="R8" t="n">
-        <v>6918856</v>
+        <v>6918898</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117579975</v>
+        <v>117579880</v>
       </c>
       <c r="B9" t="n">
-        <v>78217</v>
+        <v>90464</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1436,25 +1436,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>482221</v>
+        <v>482357</v>
       </c>
       <c r="R9" t="n">
-        <v>6918908</v>
+        <v>6918836</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,17 +1523,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu, Marielle Löthman</t>
+          <t>Marielle Löthman, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117579619</v>
+        <v>117579661</v>
       </c>
       <c r="B10" t="n">
-        <v>78217</v>
+        <v>90648</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1542,25 +1542,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1573,10 +1573,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>482087</v>
+        <v>482261</v>
       </c>
       <c r="R10" t="n">
-        <v>6918779</v>
+        <v>6918909</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1636,10 +1636,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117579838</v>
+        <v>117579703</v>
       </c>
       <c r="B11" t="n">
-        <v>78480</v>
+        <v>79098</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1652,21 +1652,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1679,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>482193</v>
+        <v>482319</v>
       </c>
       <c r="R11" t="n">
-        <v>6918714</v>
+        <v>6918649</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117579697</v>
+        <v>117579967</v>
       </c>
       <c r="B12" t="n">
-        <v>91962</v>
+        <v>91772</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1754,25 +1754,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>482321</v>
+        <v>482221</v>
       </c>
       <c r="R12" t="n">
-        <v>6918867</v>
+        <v>6918905</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1848,10 +1848,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117579705</v>
+        <v>117579889</v>
       </c>
       <c r="B13" t="n">
-        <v>79098</v>
+        <v>56499</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1860,30 +1860,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1891,10 +1896,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>482242</v>
+        <v>482358</v>
       </c>
       <c r="R13" t="n">
-        <v>6918749</v>
+        <v>6918807</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1935,7 +1940,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1954,10 +1958,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117579644</v>
+        <v>117579915</v>
       </c>
       <c r="B14" t="n">
-        <v>91772</v>
+        <v>78216</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1966,25 +1970,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1997,10 +2001,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>482260</v>
+        <v>482356</v>
       </c>
       <c r="R14" t="n">
-        <v>6918704</v>
+        <v>6918816</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2060,10 +2064,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117579967</v>
+        <v>117579705</v>
       </c>
       <c r="B15" t="n">
-        <v>91772</v>
+        <v>79098</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2072,25 +2076,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2103,10 +2107,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>482221</v>
+        <v>482242</v>
       </c>
       <c r="R15" t="n">
-        <v>6918905</v>
+        <v>6918749</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,17 +2163,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu, Marielle Löthman</t>
+          <t>Marielle Löthman, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117579889</v>
+        <v>117579838</v>
       </c>
       <c r="B16" t="n">
-        <v>56499</v>
+        <v>78480</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2178,35 +2182,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2214,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>482358</v>
+        <v>482193</v>
       </c>
       <c r="R16" t="n">
-        <v>6918807</v>
+        <v>6918714</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2258,6 +2257,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2269,14 +2269,14 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu, Marielle Löthman</t>
+          <t>Marielle Löthman, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117579646</v>
+        <v>117579955</v>
       </c>
       <c r="B17" t="n">
         <v>91772</v>
@@ -2319,10 +2319,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>482363</v>
+        <v>482213</v>
       </c>
       <c r="R17" t="n">
-        <v>6918799</v>
+        <v>6918907</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2382,10 +2382,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117579701</v>
+        <v>117579644</v>
       </c>
       <c r="B18" t="n">
-        <v>91962</v>
+        <v>91772</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2394,25 +2394,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2425,10 +2425,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>482297</v>
+        <v>482260</v>
       </c>
       <c r="R18" t="n">
-        <v>6918898</v>
+        <v>6918704</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2488,10 +2488,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117579955</v>
+        <v>117579813</v>
       </c>
       <c r="B19" t="n">
-        <v>91772</v>
+        <v>78514</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2500,25 +2500,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>482213</v>
+        <v>482200</v>
       </c>
       <c r="R19" t="n">
-        <v>6918907</v>
+        <v>6918933</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2587,17 +2587,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu, Marielle Löthman</t>
+          <t>Marielle Löthman, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117579661</v>
+        <v>117579619</v>
       </c>
       <c r="B20" t="n">
-        <v>90648</v>
+        <v>78217</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2606,25 +2606,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2637,10 +2637,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>482261</v>
+        <v>482087</v>
       </c>
       <c r="R20" t="n">
-        <v>6918909</v>
+        <v>6918779</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2700,7 +2700,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117579645</v>
+        <v>117579650</v>
       </c>
       <c r="B21" t="n">
         <v>91772</v>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>482353</v>
+        <v>482235</v>
       </c>
       <c r="R21" t="n">
-        <v>6918745</v>
+        <v>6918743</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2806,10 +2806,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117579809</v>
+        <v>117579652</v>
       </c>
       <c r="B22" t="n">
-        <v>79069</v>
+        <v>78125</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2822,21 +2822,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>482297</v>
+        <v>482237</v>
       </c>
       <c r="R22" t="n">
-        <v>6918901</v>
+        <v>6918837</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2912,7 +2912,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117579650</v>
+        <v>117579645</v>
       </c>
       <c r="B23" t="n">
         <v>91772</v>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>482235</v>
+        <v>482353</v>
       </c>
       <c r="R23" t="n">
-        <v>6918743</v>
+        <v>6918745</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 20004-2024 artfynd.xlsx
+++ b/artfynd/A 20004-2024 artfynd.xlsx
@@ -788,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117579697</v>
+        <v>117579880</v>
       </c>
       <c r="B3" t="n">
-        <v>91962</v>
+        <v>90466</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -800,25 +800,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2079</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482321</v>
+        <v>482357</v>
       </c>
       <c r="R3" t="n">
-        <v>6918867</v>
+        <v>6918836</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117579975</v>
+        <v>117579661</v>
       </c>
       <c r="B4" t="n">
-        <v>78217</v>
+        <v>90650</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -906,25 +906,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>482221</v>
+        <v>482261</v>
       </c>
       <c r="R4" t="n">
-        <v>6918908</v>
+        <v>6918909</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,17 +993,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Sebastian Kirppu</t>
+          <t>Sebastian Kirppu, Marielle Löthman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117579646</v>
+        <v>117579955</v>
       </c>
       <c r="B5" t="n">
-        <v>91772</v>
+        <v>91774</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>482363</v>
+        <v>482213</v>
       </c>
       <c r="R5" t="n">
-        <v>6918799</v>
+        <v>6918907</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,10 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117579809</v>
+        <v>117579813</v>
       </c>
       <c r="B6" t="n">
-        <v>79069</v>
+        <v>78516</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1122,21 +1122,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1149,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>482297</v>
+        <v>482200</v>
       </c>
       <c r="R6" t="n">
-        <v>6918901</v>
+        <v>6918933</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,10 +1212,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117579655</v>
+        <v>117579652</v>
       </c>
       <c r="B7" t="n">
-        <v>90425</v>
+        <v>78127</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1228,21 +1228,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3242</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482226</v>
+        <v>482237</v>
       </c>
       <c r="R7" t="n">
-        <v>6918856</v>
+        <v>6918837</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,17 +1311,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Sebastian Kirppu</t>
+          <t>Sebastian Kirppu, Marielle Löthman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117579701</v>
+        <v>117579809</v>
       </c>
       <c r="B8" t="n">
-        <v>91962</v>
+        <v>79071</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1334,21 +1334,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2079</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1364,7 +1364,7 @@
         <v>482297</v>
       </c>
       <c r="R8" t="n">
-        <v>6918898</v>
+        <v>6918901</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117579880</v>
+        <v>117579644</v>
       </c>
       <c r="B9" t="n">
-        <v>90464</v>
+        <v>91774</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1440,21 +1440,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>482357</v>
+        <v>482260</v>
       </c>
       <c r="R9" t="n">
-        <v>6918836</v>
+        <v>6918704</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,17 +1523,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Sebastian Kirppu</t>
+          <t>Sebastian Kirppu, Marielle Löthman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117579661</v>
+        <v>117579650</v>
       </c>
       <c r="B10" t="n">
-        <v>90648</v>
+        <v>91774</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1542,25 +1542,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1573,10 +1573,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>482261</v>
+        <v>482235</v>
       </c>
       <c r="R10" t="n">
-        <v>6918909</v>
+        <v>6918743</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,17 +1629,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Sebastian Kirppu</t>
+          <t>Sebastian Kirppu, Marielle Löthman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117579703</v>
+        <v>117579701</v>
       </c>
       <c r="B11" t="n">
-        <v>79098</v>
+        <v>91964</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1652,21 +1652,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1679,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>482319</v>
+        <v>482297</v>
       </c>
       <c r="R11" t="n">
-        <v>6918649</v>
+        <v>6918898</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117579967</v>
+        <v>117579838</v>
       </c>
       <c r="B12" t="n">
-        <v>91772</v>
+        <v>78482</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1754,25 +1754,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>482221</v>
+        <v>482193</v>
       </c>
       <c r="R12" t="n">
-        <v>6918905</v>
+        <v>6918714</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1848,10 +1848,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117579889</v>
+        <v>117579619</v>
       </c>
       <c r="B13" t="n">
-        <v>56499</v>
+        <v>78219</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1860,35 +1860,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1896,10 +1891,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>482358</v>
+        <v>482087</v>
       </c>
       <c r="R13" t="n">
-        <v>6918807</v>
+        <v>6918779</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1940,6 +1935,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1951,7 +1947,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Sebastian Kirppu</t>
+          <t>Sebastian Kirppu, Marielle Löthman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1961,7 +1957,7 @@
         <v>117579915</v>
       </c>
       <c r="B14" t="n">
-        <v>78216</v>
+        <v>78218</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2064,10 +2060,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117579705</v>
+        <v>117579646</v>
       </c>
       <c r="B15" t="n">
-        <v>79098</v>
+        <v>91774</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2076,25 +2072,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2107,10 +2103,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>482242</v>
+        <v>482363</v>
       </c>
       <c r="R15" t="n">
-        <v>6918749</v>
+        <v>6918799</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2163,17 +2159,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Sebastian Kirppu</t>
+          <t>Sebastian Kirppu, Marielle Löthman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117579838</v>
+        <v>117579967</v>
       </c>
       <c r="B16" t="n">
-        <v>78480</v>
+        <v>91774</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2182,25 +2178,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2213,10 +2209,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>482193</v>
+        <v>482221</v>
       </c>
       <c r="R16" t="n">
-        <v>6918714</v>
+        <v>6918905</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2276,10 +2272,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117579955</v>
+        <v>117579645</v>
       </c>
       <c r="B17" t="n">
-        <v>91772</v>
+        <v>91774</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2319,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>482213</v>
+        <v>482353</v>
       </c>
       <c r="R17" t="n">
-        <v>6918907</v>
+        <v>6918745</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2375,17 +2371,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Sebastian Kirppu</t>
+          <t>Sebastian Kirppu, Marielle Löthman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117579644</v>
+        <v>117579697</v>
       </c>
       <c r="B18" t="n">
-        <v>91772</v>
+        <v>91964</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2394,25 +2390,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2425,10 +2421,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>482260</v>
+        <v>482321</v>
       </c>
       <c r="R18" t="n">
-        <v>6918704</v>
+        <v>6918867</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2488,10 +2484,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117579813</v>
+        <v>117579705</v>
       </c>
       <c r="B19" t="n">
-        <v>78514</v>
+        <v>79100</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2504,21 +2500,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2531,10 +2527,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>482200</v>
+        <v>482242</v>
       </c>
       <c r="R19" t="n">
-        <v>6918933</v>
+        <v>6918749</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2594,10 +2590,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117579619</v>
+        <v>117579703</v>
       </c>
       <c r="B20" t="n">
-        <v>78217</v>
+        <v>79100</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2610,21 +2606,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2637,10 +2633,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>482087</v>
+        <v>482319</v>
       </c>
       <c r="R20" t="n">
-        <v>6918779</v>
+        <v>6918649</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2700,10 +2696,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117579650</v>
+        <v>117579889</v>
       </c>
       <c r="B21" t="n">
-        <v>91772</v>
+        <v>56500</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2716,26 +2712,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2743,10 +2744,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>482235</v>
+        <v>482358</v>
       </c>
       <c r="R21" t="n">
-        <v>6918743</v>
+        <v>6918807</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2787,7 +2788,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2806,10 +2806,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117579652</v>
+        <v>117579655</v>
       </c>
       <c r="B22" t="n">
-        <v>78125</v>
+        <v>90427</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2822,21 +2822,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>3242</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>482237</v>
+        <v>482226</v>
       </c>
       <c r="R22" t="n">
-        <v>6918837</v>
+        <v>6918856</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2905,17 +2905,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Sebastian Kirppu</t>
+          <t>Sebastian Kirppu, Marielle Löthman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117579645</v>
+        <v>117579975</v>
       </c>
       <c r="B23" t="n">
-        <v>91772</v>
+        <v>78219</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2924,25 +2924,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>482353</v>
+        <v>482221</v>
       </c>
       <c r="R23" t="n">
-        <v>6918745</v>
+        <v>6918908</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
